--- a/research/traditional_assets/database/data/japan/japan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08599999999999999</v>
+        <v>0.09315000000000001</v>
       </c>
       <c r="E2">
-        <v>0.132</v>
+        <v>0.0888</v>
       </c>
       <c r="G2">
-        <v>0.1026880446738303</v>
+        <v>0.09168434185901435</v>
       </c>
       <c r="H2">
-        <v>0.1025890515272019</v>
+        <v>0.09161987939280516</v>
       </c>
       <c r="I2">
-        <v>0.07758693628902615</v>
+        <v>0.08947962136786891</v>
       </c>
       <c r="J2">
-        <v>0.05793509327453254</v>
+        <v>0.06355030809897945</v>
       </c>
       <c r="K2">
-        <v>99.95</v>
+        <v>86.02</v>
       </c>
       <c r="L2">
-        <v>0.08456722226922751</v>
+        <v>0.08943647327926804</v>
       </c>
       <c r="M2">
-        <v>15.97462</v>
+        <v>7.306229999999999</v>
       </c>
       <c r="N2">
-        <v>0.02147414975131066</v>
+        <v>0.00942265182682263</v>
       </c>
       <c r="O2">
-        <v>0.1598261130565282</v>
+        <v>0.0849364101371774</v>
       </c>
       <c r="P2">
-        <v>13.19462</v>
+        <v>5.25623</v>
       </c>
       <c r="Q2">
-        <v>0.01773708831832235</v>
+        <v>0.006778820980409858</v>
       </c>
       <c r="R2">
-        <v>0.1320122061030515</v>
+        <v>0.06110474308300395</v>
       </c>
       <c r="S2">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="T2">
-        <v>0.1740260488199407</v>
+        <v>0.2805824618168331</v>
       </c>
       <c r="U2">
-        <v>392.7</v>
+        <v>253.1</v>
       </c>
       <c r="V2">
-        <v>0.5278935340771609</v>
+        <v>0.3264163840132063</v>
       </c>
       <c r="W2">
-        <v>0.175101319377206</v>
+        <v>0.1557640088866946</v>
       </c>
       <c r="X2">
-        <v>0.04948038568506716</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y2">
-        <v>0.1256209336921389</v>
+        <v>0.07332145168819312</v>
       </c>
       <c r="Z2">
-        <v>5.141266285316571</v>
+        <v>6.881772705493388</v>
       </c>
       <c r="AA2">
-        <v>0.2694008233388328</v>
+        <v>0.5545876490791573</v>
       </c>
       <c r="AB2">
-        <v>0.04876297606564305</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC2">
-        <v>0.2213780519881398</v>
+        <v>0.4721450918806557</v>
       </c>
       <c r="AD2">
-        <v>96.8</v>
+        <v>22.7</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.03250084191841559</v>
       </c>
       <c r="AF2">
-        <v>96.8</v>
+        <v>22.73250084191842</v>
       </c>
       <c r="AG2">
-        <v>-295.9</v>
+        <v>-230.3674991580816</v>
       </c>
       <c r="AH2">
-        <v>0.1151421434518853</v>
+        <v>0.02848247082113147</v>
       </c>
       <c r="AI2">
-        <v>0.1391804457225018</v>
+        <v>0.05554910911315841</v>
       </c>
       <c r="AJ2">
-        <v>-0.6604910714285713</v>
+        <v>-0.4226752084587767</v>
       </c>
       <c r="AK2">
-        <v>-0.9772126816380446</v>
+        <v>-1.475461533734895</v>
       </c>
       <c r="AL2">
-        <v>1.479</v>
+        <v>0.177</v>
       </c>
       <c r="AM2">
-        <v>1.362</v>
+        <v>0.163</v>
       </c>
       <c r="AN2">
-        <v>0.7255284065357517</v>
+        <v>0.2616473408792273</v>
       </c>
       <c r="AO2">
-        <v>62.00135226504396</v>
+        <v>486.1016949152542</v>
       </c>
       <c r="AP2">
-        <v>-2.217808424524059</v>
+        <v>-2.655288263423334</v>
       </c>
       <c r="AQ2">
-        <v>67.32745961820852</v>
+        <v>527.8527607361964</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SBI Insurance Group Co., Ltd. (TSE:7326)</t>
+          <t>FP Partner Inc. (TSE:7388)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.06182495344506517</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.06182495344506517</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.05710738671632527</v>
+        <v>0.08292682926829269</v>
       </c>
       <c r="J3">
-        <v>0.04805806235973834</v>
+        <v>0.05597560975609757</v>
       </c>
       <c r="K3">
-        <v>54.7</v>
+        <v>10.8</v>
       </c>
       <c r="L3">
-        <v>0.06790813159528243</v>
+        <v>0.05853658536585366</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,67 +761,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>293.3</v>
+        <v>37.2</v>
       </c>
       <c r="V3">
-        <v>1.180281690140845</v>
-      </c>
-      <c r="W3">
-        <v>0.1321575259724571</v>
+        <v>0.1027908261950815</v>
       </c>
       <c r="X3">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="Y3">
-        <v>0.08334416490456406</v>
-      </c>
-      <c r="Z3">
-        <v>8.355809128630707</v>
-      </c>
-      <c r="AA3">
-        <v>0.4015639961698054</v>
+        <v>0.08347984877075527</v>
       </c>
       <c r="AB3">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="AC3">
-        <v>0.3527506351019123</v>
+        <v>0.0825284099244087</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="AG3">
-        <v>-293.3</v>
+        <v>-26</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0300187617260788</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ3">
-        <v>6.546874999999998</v>
+        <v>-0.07740398928252458</v>
       </c>
       <c r="AK3">
-        <v>-2.60248447204969</v>
+        <v>-3.421052631578949</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>-4.792483660130719</v>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AO3">
+        <v>215.4929577464789</v>
+      </c>
+      <c r="AQ3">
+        <v>215.4929577464789</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Advance Create Co., Ltd. (TSE:8798)</t>
+          <t>Agent Insurance Group, Inc. (NSE:5836)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,122 +825,86 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.173</v>
-      </c>
       <c r="G4">
-        <v>0.2257085020242915</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.2257085020242915</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.1852226720647773</v>
+        <v>0.07182539682539683</v>
       </c>
       <c r="J4">
-        <v>0.1259730804744655</v>
+        <v>0.05080701754385965</v>
       </c>
       <c r="K4">
-        <v>11.6</v>
+        <v>1.35</v>
       </c>
       <c r="L4">
-        <v>0.1174089068825911</v>
+        <v>0.05357142857142858</v>
       </c>
       <c r="M4">
-        <v>5.918</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02812737642585551</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5101724137931035</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>5.918</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02812737642585551</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.5101724137931035</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>29.9</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.1421102661596958</v>
-      </c>
-      <c r="W4">
-        <v>0.2180451127819549</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.05014741030224123</v>
-      </c>
-      <c r="Y4">
-        <v>0.1678977024797136</v>
-      </c>
-      <c r="Z4">
-        <v>2.292343387470997</v>
-      </c>
-      <c r="AA4">
-        <v>0.2887735580249928</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AB4">
-        <v>0.04871259106339301</v>
-      </c>
-      <c r="AC4">
-        <v>0.2400609669615998</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-17.9</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.0539568345323741</v>
-      </c>
-      <c r="AI4">
-        <v>0.1659751037344398</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.09298701298701298</v>
-      </c>
-      <c r="AK4">
-        <v>-0.4221698113207547</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>0.099</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM4">
-        <v>0.07200000000000001</v>
-      </c>
-      <c r="AN4">
-        <v>0.5381165919282511</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AO4">
-        <v>184.8484848484848</v>
-      </c>
-      <c r="AP4">
-        <v>-0.8026905829596411</v>
+        <v>201.1111111111111</v>
       </c>
       <c r="AQ4">
-        <v>254.1666666666667</v>
+        <v>201.1111111111111</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +915,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NFC Holdings, Inc. (JASDAQ:7169)</t>
+          <t>SBI Insurance Group Co., Ltd. (TSE:7326)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,122 +923,107 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.0236</v>
-      </c>
-      <c r="E5">
-        <v>0.132</v>
-      </c>
       <c r="G5">
-        <v>0.1881145788798632</v>
+        <v>0.1039596150812431</v>
       </c>
       <c r="H5">
-        <v>0.1881145788798632</v>
+        <v>0.1039596150812431</v>
       </c>
       <c r="I5">
-        <v>0.1004702864471997</v>
+        <v>0.08187411263606247</v>
       </c>
       <c r="J5">
-        <v>0.0813473174282531</v>
+        <v>0.07209027020685055</v>
       </c>
       <c r="K5">
-        <v>31.1</v>
+        <v>63.1</v>
       </c>
       <c r="L5">
-        <v>0.1329628046173578</v>
+        <v>0.09954251459220698</v>
       </c>
       <c r="M5">
-        <v>9.1343</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04440593096742829</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.2937073954983923</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>6.354299999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03089110354885756</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.2043183279742765</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>2.78</v>
-      </c>
-      <c r="T5">
-        <v>0.3043473500979824</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>53</v>
+        <v>185.9</v>
       </c>
       <c r="V5">
-        <v>0.2576567817209529</v>
+        <v>1.025938189845475</v>
       </c>
       <c r="W5">
-        <v>0.3554285714285714</v>
+        <v>0.1557640088866946</v>
       </c>
       <c r="X5">
-        <v>0.05845604447224445</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y5">
-        <v>0.296972526956327</v>
+        <v>0.07332145168819312</v>
       </c>
       <c r="Z5">
-        <v>3.07358738501971</v>
+        <v>7.692961165048543</v>
       </c>
       <c r="AA5">
-        <v>0.2500280886526727</v>
+        <v>0.5545876490791573</v>
       </c>
       <c r="AB5">
-        <v>0.04733295163799295</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC5">
-        <v>0.2026951370146798</v>
+        <v>0.4721450918806557</v>
       </c>
       <c r="AD5">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>84.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>31.8</v>
+        <v>-185.9</v>
       </c>
       <c r="AH5">
-        <v>0.2919104991394148</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.4581307401404646</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.1338947368421053</v>
+        <v>39.55319148936156</v>
       </c>
       <c r="AK5">
-        <v>0.2407267221801665</v>
+        <v>-2.036144578313253</v>
       </c>
       <c r="AL5">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.922902494331066</v>
-      </c>
-      <c r="AO5">
-        <v>17.02898550724638</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.7210884353741496</v>
-      </c>
-      <c r="AQ5">
-        <v>18.2170542635659</v>
+        <v>-2.868827160493828</v>
       </c>
     </row>
     <row r="6">
@@ -1100,124 +1034,258 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Advance Create Co., Ltd. (TSE:8798)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.121</v>
+      </c>
+      <c r="G6">
+        <v>0.2121951219512195</v>
+      </c>
+      <c r="H6">
+        <v>0.2121951219512195</v>
+      </c>
+      <c r="I6">
+        <v>0.1734329247758087</v>
+      </c>
+      <c r="J6">
+        <v>0.1150268368733673</v>
+      </c>
+      <c r="K6">
+        <v>9.07</v>
+      </c>
+      <c r="L6">
+        <v>0.110609756097561</v>
+      </c>
+      <c r="M6">
+        <v>6.583299999999999</v>
+      </c>
+      <c r="N6">
+        <v>0.03717278373800113</v>
+      </c>
+      <c r="O6">
+        <v>0.7258324145534729</v>
+      </c>
+      <c r="P6">
+        <v>4.5333</v>
+      </c>
+      <c r="Q6">
+        <v>0.0255974025974026</v>
+      </c>
+      <c r="R6">
+        <v>0.4998125689084895</v>
+      </c>
+      <c r="S6">
+        <v>2.05</v>
+      </c>
+      <c r="T6">
+        <v>0.3113939817416797</v>
+      </c>
+      <c r="U6">
+        <v>15.7</v>
+      </c>
+      <c r="V6">
+        <v>0.08865047995482778</v>
+      </c>
+      <c r="W6">
+        <v>0.1504145936981758</v>
+      </c>
+      <c r="X6">
+        <v>0.08462516821839891</v>
+      </c>
+      <c r="Y6">
+        <v>0.0657894254797769</v>
+      </c>
+      <c r="Z6">
+        <v>1.932480960891032</v>
+      </c>
+      <c r="AA6">
+        <v>0.2222871722493007</v>
+      </c>
+      <c r="AB6">
+        <v>0.08207744274041617</v>
+      </c>
+      <c r="AC6">
+        <v>0.1402097295088845</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>0.03250084191841559</v>
+      </c>
+      <c r="AF6">
+        <v>11.53250084191841</v>
+      </c>
+      <c r="AG6">
+        <v>-4.167499158081585</v>
+      </c>
+      <c r="AH6">
+        <v>0.06113740098045518</v>
+      </c>
+      <c r="AI6">
+        <v>0.189266822837914</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.02409899317821809</v>
+      </c>
+      <c r="AK6">
+        <v>-0.09213505953708907</v>
+      </c>
+      <c r="AL6">
+        <v>0.097</v>
+      </c>
+      <c r="AM6">
+        <v>0.083</v>
+      </c>
+      <c r="AN6">
+        <v>0.6598577002524674</v>
+      </c>
+      <c r="AO6">
+        <v>146.3917525773196</v>
+      </c>
+      <c r="AP6">
+        <v>-0.2391266443700703</v>
+      </c>
+      <c r="AQ6">
+        <v>171.0843373493976</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>IRRC Corporation (TSE:7325)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.124</v>
-      </c>
-      <c r="E6">
-        <v>0.105</v>
-      </c>
-      <c r="G6">
-        <v>0.1205263157894737</v>
-      </c>
-      <c r="H6">
-        <v>0.1178489702517162</v>
-      </c>
-      <c r="I6">
-        <v>0.08924485125858123</v>
-      </c>
-      <c r="J6">
-        <v>0.05850240892272034</v>
-      </c>
-      <c r="K6">
-        <v>2.55</v>
-      </c>
-      <c r="L6">
-        <v>0.05835240274599542</v>
-      </c>
-      <c r="M6">
-        <v>0.9223199999999999</v>
-      </c>
-      <c r="N6">
-        <v>0.01163076923076923</v>
-      </c>
-      <c r="O6">
-        <v>0.3616941176470588</v>
-      </c>
-      <c r="P6">
-        <v>0.9223199999999999</v>
-      </c>
-      <c r="Q6">
-        <v>0.01163076923076923</v>
-      </c>
-      <c r="R6">
-        <v>0.3616941176470588</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>16.5</v>
-      </c>
-      <c r="V6">
-        <v>0.2080706179066835</v>
-      </c>
-      <c r="W6">
-        <v>0.07919254658385091</v>
-      </c>
-      <c r="X6">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="Y6">
-        <v>0.03037918551595784</v>
-      </c>
-      <c r="Z6">
-        <v>3.059152957647882</v>
-      </c>
-      <c r="AA6">
-        <v>0.1789678172854658</v>
-      </c>
-      <c r="AB6">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="AC6">
-        <v>0.1301544562175727</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>-16.5</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.2627388535031847</v>
-      </c>
-      <c r="AK6">
-        <v>-1.057692307692307</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>-2.835051546391752</v>
+      <c r="D7">
+        <v>0.108</v>
+      </c>
+      <c r="E7">
+        <v>0.0566</v>
+      </c>
+      <c r="G7">
+        <v>0.1348618784530387</v>
+      </c>
+      <c r="H7">
+        <v>0.1331491712707182</v>
+      </c>
+      <c r="I7">
+        <v>0.07817679558011049</v>
+      </c>
+      <c r="J7">
+        <v>0.04886049723756906</v>
+      </c>
+      <c r="K7">
+        <v>1.7</v>
+      </c>
+      <c r="L7">
+        <v>0.04696132596685083</v>
+      </c>
+      <c r="M7">
+        <v>0.7229300000000001</v>
+      </c>
+      <c r="N7">
+        <v>0.01575010893246188</v>
+      </c>
+      <c r="O7">
+        <v>0.4252529411764707</v>
+      </c>
+      <c r="P7">
+        <v>0.7229300000000001</v>
+      </c>
+      <c r="Q7">
+        <v>0.01575010893246188</v>
+      </c>
+      <c r="R7">
+        <v>0.4252529411764707</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>14.3</v>
+      </c>
+      <c r="V7">
+        <v>0.3115468409586057</v>
+      </c>
+      <c r="W7">
+        <v>0.0529595015576324</v>
+      </c>
+      <c r="X7">
+        <v>0.08244255719850152</v>
+      </c>
+      <c r="Y7">
+        <v>-0.02948305564086912</v>
+      </c>
+      <c r="Z7">
+        <v>2.42497320471597</v>
+      </c>
+      <c r="AA7">
+        <v>0.1184853965702036</v>
+      </c>
+      <c r="AB7">
+        <v>0.08244255719850152</v>
+      </c>
+      <c r="AC7">
+        <v>0.03604283937170212</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-14.3</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.4525316455696203</v>
+      </c>
+      <c r="AK7">
+        <v>-1.191666666666667</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>-3.15673289183223</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09315000000000001</v>
+        <v>0.0143</v>
       </c>
       <c r="E2">
-        <v>0.0888</v>
+        <v>-0.07550000000000001</v>
       </c>
       <c r="G2">
-        <v>0.09168434185901435</v>
+        <v>0.08831617148083674</v>
       </c>
       <c r="H2">
-        <v>0.09161987939280516</v>
+        <v>0.08812144100551736</v>
       </c>
       <c r="I2">
-        <v>0.08947962136786891</v>
+        <v>0.07410250994000042</v>
       </c>
       <c r="J2">
-        <v>0.06355030809897945</v>
+        <v>0.05693235228883577</v>
       </c>
       <c r="K2">
-        <v>86.02</v>
+        <v>88.82299999999999</v>
       </c>
       <c r="L2">
-        <v>0.08943647327926804</v>
+        <v>0.08735628792572704</v>
       </c>
       <c r="M2">
-        <v>7.306229999999999</v>
+        <v>2.6846</v>
       </c>
       <c r="N2">
-        <v>0.00942265182682263</v>
+        <v>0.002135550075570758</v>
       </c>
       <c r="O2">
-        <v>0.0849364101371774</v>
+        <v>0.03022415365389595</v>
       </c>
       <c r="P2">
-        <v>5.25623</v>
+        <v>2.4976</v>
       </c>
       <c r="Q2">
-        <v>0.006778820980409858</v>
+        <v>0.001986795004375149</v>
       </c>
       <c r="R2">
-        <v>0.06110474308300395</v>
+        <v>0.02811884309244228</v>
       </c>
       <c r="S2">
-        <v>2.05</v>
+        <v>0.187</v>
       </c>
       <c r="T2">
-        <v>0.2805824618168331</v>
+        <v>0.0696565596364449</v>
       </c>
       <c r="U2">
-        <v>253.1</v>
+        <v>292.046</v>
       </c>
       <c r="V2">
-        <v>0.3264163840132063</v>
+        <v>0.2323172380876621</v>
       </c>
       <c r="W2">
-        <v>0.1557640088866946</v>
+        <v>0.1669280289330922</v>
       </c>
       <c r="X2">
-        <v>0.08244255719850152</v>
+        <v>0.0752541085205567</v>
       </c>
       <c r="Y2">
-        <v>0.07332145168819312</v>
+        <v>0.09167392041253555</v>
       </c>
       <c r="Z2">
-        <v>6.881772705493388</v>
+        <v>6.607228551341016</v>
       </c>
       <c r="AA2">
-        <v>0.5545876490791573</v>
+        <v>0.3650389456008183</v>
       </c>
       <c r="AB2">
-        <v>0.08244255719850152</v>
+        <v>0.07348052147201668</v>
       </c>
       <c r="AC2">
-        <v>0.4721450918806557</v>
+        <v>0.2911852146121915</v>
       </c>
       <c r="AD2">
-        <v>22.7</v>
+        <v>28.74</v>
       </c>
       <c r="AE2">
-        <v>0.03250084191841559</v>
+        <v>10.7415445905349</v>
       </c>
       <c r="AF2">
-        <v>22.73250084191842</v>
+        <v>39.4815445905349</v>
       </c>
       <c r="AG2">
-        <v>-230.3674991580816</v>
+        <v>-252.5644554094651</v>
       </c>
       <c r="AH2">
-        <v>0.02848247082113147</v>
+        <v>0.03045049095080503</v>
       </c>
       <c r="AI2">
-        <v>0.05554910911315841</v>
+        <v>0.08708238141054483</v>
       </c>
       <c r="AJ2">
-        <v>-0.4226752084587767</v>
+        <v>-0.2514241101467589</v>
       </c>
       <c r="AK2">
-        <v>-1.475461533734895</v>
+        <v>-1.565460705205828</v>
       </c>
       <c r="AL2">
-        <v>0.177</v>
+        <v>0.218</v>
       </c>
       <c r="AM2">
-        <v>0.163</v>
+        <v>0.08099999999999999</v>
       </c>
       <c r="AN2">
-        <v>0.2616473408792273</v>
+        <v>0.4614643545279383</v>
       </c>
       <c r="AO2">
-        <v>486.1016949152542</v>
+        <v>334.3256880733945</v>
       </c>
       <c r="AP2">
-        <v>-2.655288263423334</v>
+        <v>-4.055305963543113</v>
       </c>
       <c r="AQ2">
-        <v>527.8527607361964</v>
+        <v>899.7901234567902</v>
       </c>
     </row>
     <row r="3">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1420586797066015</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.141320293398533</v>
       </c>
       <c r="I3">
-        <v>0.08292682926829269</v>
+        <v>0.1726161369193154</v>
       </c>
       <c r="J3">
-        <v>0.05597560975609757</v>
+        <v>0.117802099011789</v>
       </c>
       <c r="K3">
-        <v>10.8</v>
+        <v>24.5</v>
       </c>
       <c r="L3">
-        <v>0.05853658536585366</v>
+        <v>0.1198044009779951</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,52 +761,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>37.2</v>
+        <v>74.5</v>
       </c>
       <c r="V3">
-        <v>0.1027908261950815</v>
+        <v>0.08726718987934871</v>
+      </c>
+      <c r="W3">
+        <v>0.7291666666666666</v>
       </c>
       <c r="X3">
-        <v>0.08347984877075527</v>
+        <v>0.07398050296893791</v>
+      </c>
+      <c r="Y3">
+        <v>0.6551861636977288</v>
+      </c>
+      <c r="Z3">
+        <v>26.90789473684212</v>
+      </c>
+      <c r="AA3">
+        <v>3.169806479988273</v>
       </c>
       <c r="AB3">
-        <v>0.0825284099244087</v>
+        <v>0.07380747562126123</v>
+      </c>
+      <c r="AC3">
+        <v>3.095999004367012</v>
       </c>
       <c r="AD3">
-        <v>11.2</v>
+        <v>4.45</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.2</v>
+        <v>4.45</v>
       </c>
       <c r="AG3">
-        <v>-26</v>
+        <v>-70.05</v>
       </c>
       <c r="AH3">
-        <v>0.0300187617260788</v>
+        <v>0.005185573617665909</v>
       </c>
       <c r="AI3">
-        <v>0.25</v>
+        <v>0.05201636469900643</v>
       </c>
       <c r="AJ3">
-        <v>-0.07740398928252458</v>
+        <v>-0.08938939577617558</v>
       </c>
       <c r="AK3">
-        <v>-3.421052631578949</v>
+        <v>-6.339366515837106</v>
       </c>
       <c r="AL3">
-        <v>0.07099999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="AM3">
-        <v>0.07099999999999999</v>
+        <v>0.021</v>
       </c>
       <c r="AO3">
-        <v>215.4929577464789</v>
+        <v>1680.952380952381</v>
       </c>
       <c r="AQ3">
-        <v>215.4929577464789</v>
+        <v>1680.952380952381</v>
       </c>
     </row>
     <row r="4">
@@ -826,22 +841,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.08991228070175437</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.08991228070175437</v>
       </c>
       <c r="I4">
-        <v>0.07182539682539683</v>
+        <v>0.04291403816214995</v>
       </c>
       <c r="J4">
-        <v>0.05080701754385965</v>
+        <v>0.02751321476040776</v>
       </c>
       <c r="K4">
-        <v>1.35</v>
+        <v>0.502</v>
       </c>
       <c r="L4">
-        <v>0.05357142857142858</v>
+        <v>0.02201754385964912</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -865,46 +880,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>6.87</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.2935897435897436</v>
       </c>
       <c r="X4">
-        <v>0.08244255719850152</v>
+        <v>0.0765277140721755</v>
+      </c>
+      <c r="Z4">
+        <v>75.29731304684898</v>
+      </c>
+      <c r="AA4">
+        <v>2.071671144739609</v>
       </c>
       <c r="AB4">
-        <v>0.08244255719850152</v>
+        <v>0.07315356732277213</v>
+      </c>
+      <c r="AC4">
+        <v>1.998517577416837</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.3027996495149056</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.572799649514906</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-4.297200350485094</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.09905746335524357</v>
+      </c>
+      <c r="AI4">
+        <v>0.2480332925002774</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.224951338512008</v>
+      </c>
+      <c r="AK4">
+        <v>-1.226790219383573</v>
       </c>
       <c r="AL4">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="AM4">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
+      </c>
+      <c r="AN4">
+        <v>1.798732171156894</v>
       </c>
       <c r="AO4">
-        <v>201.1111111111111</v>
+        <v>122.4285714285714</v>
+      </c>
+      <c r="AP4">
+        <v>-3.40507159309437</v>
       </c>
       <c r="AQ4">
-        <v>201.1111111111111</v>
+        <v>122.4285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -924,70 +960,73 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1039596150812431</v>
+        <v>0.096</v>
       </c>
       <c r="H5">
-        <v>0.1039596150812431</v>
+        <v>0.096</v>
       </c>
       <c r="I5">
-        <v>0.08187411263606247</v>
+        <v>0.07288888888888889</v>
       </c>
       <c r="J5">
-        <v>0.07209027020685055</v>
+        <v>0.06962272855133615</v>
       </c>
       <c r="K5">
-        <v>63.1</v>
+        <v>75.5</v>
       </c>
       <c r="L5">
-        <v>0.09954251459220698</v>
+        <v>0.1118518518518519</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>1.6616</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.009144744083654377</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.02200794701986755</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>1.6616</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.009144744083654377</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.02200794701986755</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>185.9</v>
+        <v>193.9</v>
       </c>
       <c r="V5">
-        <v>1.025938189845475</v>
+        <v>1.067143643368189</v>
       </c>
       <c r="W5">
-        <v>0.1557640088866946</v>
+        <v>0.2730560578661845</v>
       </c>
       <c r="X5">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y5">
-        <v>0.07332145168819312</v>
+        <v>0.1992023268775577</v>
       </c>
       <c r="Z5">
-        <v>7.692961165048543</v>
+        <v>9.882869692532942</v>
       </c>
       <c r="AA5">
-        <v>0.5545876490791573</v>
+        <v>0.6880723539114481</v>
       </c>
       <c r="AB5">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC5">
-        <v>0.4721450918806557</v>
+        <v>0.6142186229228213</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -999,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-185.9</v>
+        <v>-193.9</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1008,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>39.55319148936156</v>
+        <v>15.8934426229508</v>
       </c>
       <c r="AK5">
-        <v>-2.036144578313253</v>
+        <v>-2.674482758620691</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1023,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>-2.868827160493828</v>
+        <v>-3.072900158478606</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Advance Create Co., Ltd. (TSE:8798)</t>
+          <t>IRRC Corporation (TSE:7325)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1043,121 +1082,115 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.07829999999999999</v>
+        <v>0.128</v>
       </c>
       <c r="E6">
-        <v>0.121</v>
+        <v>-0.375</v>
       </c>
       <c r="G6">
-        <v>0.2121951219512195</v>
+        <v>0.07642685851318945</v>
       </c>
       <c r="H6">
-        <v>0.2121951219512195</v>
+        <v>0.07529976019184652</v>
       </c>
       <c r="I6">
-        <v>0.1734329247758087</v>
+        <v>0.02328537170263789</v>
       </c>
       <c r="J6">
-        <v>0.1150268368733673</v>
+        <v>0.01164268585131894</v>
       </c>
       <c r="K6">
-        <v>9.07</v>
+        <v>-0.107</v>
       </c>
       <c r="L6">
-        <v>0.110609756097561</v>
+        <v>-0.002565947242206235</v>
       </c>
       <c r="M6">
-        <v>6.583299999999999</v>
+        <v>0.836</v>
       </c>
       <c r="N6">
-        <v>0.03717278373800113</v>
+        <v>0.02182767624020888</v>
       </c>
       <c r="O6">
-        <v>0.7258324145534729</v>
+        <v>-7.813084112149532</v>
       </c>
       <c r="P6">
-        <v>4.5333</v>
+        <v>0.836</v>
       </c>
       <c r="Q6">
-        <v>0.0255974025974026</v>
+        <v>0.02182767624020888</v>
       </c>
       <c r="R6">
-        <v>0.4998125689084895</v>
+        <v>-7.813084112149532</v>
       </c>
       <c r="S6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3113939817416797</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>15.7</v>
+        <v>7.87</v>
       </c>
       <c r="V6">
-        <v>0.08865047995482778</v>
+        <v>0.2054830287206267</v>
       </c>
       <c r="W6">
-        <v>0.1504145936981758</v>
+        <v>-0.004068441064638783</v>
       </c>
       <c r="X6">
-        <v>0.08462516821839891</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y6">
-        <v>0.0657894254797769</v>
+        <v>-0.07792217205326558</v>
       </c>
       <c r="Z6">
-        <v>1.932480960891032</v>
+        <v>3.607890638518775</v>
       </c>
       <c r="AA6">
-        <v>0.2222871722493007</v>
+        <v>0.04200553729018861</v>
       </c>
       <c r="AB6">
-        <v>0.08207744274041617</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC6">
-        <v>0.1402097295088845</v>
+        <v>-0.03184819369843819</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0.03250084191841559</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>11.53250084191841</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-4.167499158081585</v>
+        <v>-7.87</v>
       </c>
       <c r="AH6">
-        <v>0.06113740098045518</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.189266822837914</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.02409899317821809</v>
+        <v>-0.2586263555701611</v>
       </c>
       <c r="AK6">
-        <v>-0.09213505953708907</v>
+        <v>-0.5236194278110446</v>
       </c>
       <c r="AL6">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.6598577002524674</v>
-      </c>
-      <c r="AO6">
-        <v>146.3917525773196</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>-0.2391266443700703</v>
-      </c>
-      <c r="AQ6">
-        <v>171.0843373493976</v>
+        <v>-2.810714285714286</v>
       </c>
     </row>
     <row r="7">
@@ -1168,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IRRC Corporation (TSE:7325)</t>
+          <t>Chuou International Group Co., Ltd. (TSE:7170)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1177,115 +1210,249 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.108</v>
+        <v>0.00203</v>
       </c>
       <c r="E7">
-        <v>0.0566</v>
+        <v>0.224</v>
       </c>
       <c r="G7">
-        <v>0.1348618784530387</v>
+        <v>0.07118997912317328</v>
       </c>
       <c r="H7">
-        <v>0.1331491712707182</v>
+        <v>0.07118997912317328</v>
       </c>
       <c r="I7">
-        <v>0.07817679558011049</v>
+        <v>0.01148225469728601</v>
       </c>
       <c r="J7">
-        <v>0.04886049723756906</v>
+        <v>0.009541591931547532</v>
       </c>
       <c r="K7">
-        <v>1.7</v>
+        <v>0.228</v>
       </c>
       <c r="L7">
-        <v>0.04696132596685083</v>
+        <v>0.04759916492693111</v>
       </c>
       <c r="M7">
-        <v>0.7229300000000001</v>
+        <v>0.187</v>
       </c>
       <c r="N7">
-        <v>0.01575010893246188</v>
+        <v>0.04452380952380952</v>
       </c>
       <c r="O7">
-        <v>0.4252529411764707</v>
+        <v>0.8201754385964912</v>
       </c>
       <c r="P7">
-        <v>0.7229300000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01575010893246188</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.4252529411764707</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>14.3</v>
+        <v>0.616</v>
       </c>
       <c r="V7">
-        <v>0.3115468409586057</v>
+        <v>0.1466666666666667</v>
       </c>
       <c r="W7">
-        <v>0.0529595015576324</v>
+        <v>0.0608</v>
       </c>
       <c r="X7">
-        <v>0.08244255719850152</v>
+        <v>0.1116080681816288</v>
       </c>
       <c r="Y7">
-        <v>-0.02948305564086912</v>
+        <v>-0.05080806818162881</v>
       </c>
       <c r="Z7">
-        <v>2.42497320471597</v>
+        <v>0.4565818320465161</v>
       </c>
       <c r="AA7">
-        <v>0.1184853965702036</v>
+        <v>0.004356517524746228</v>
       </c>
       <c r="AB7">
-        <v>0.08244255719850152</v>
+        <v>0.06955475343286195</v>
       </c>
       <c r="AC7">
-        <v>0.03604283937170212</v>
+        <v>-0.06519823590811573</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="AG7">
-        <v>-14.3</v>
+        <v>5.904</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.6082089552238806</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.5863309352517986</v>
       </c>
       <c r="AJ7">
-        <v>-0.4525316455696203</v>
+        <v>0.5843230403800476</v>
       </c>
       <c r="AK7">
-        <v>-1.191666666666667</v>
+        <v>0.5620715917745621</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-0.048</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>20.50314465408805</v>
+      </c>
+      <c r="AO7">
+        <v>0.7236842105263158</v>
       </c>
       <c r="AP7">
-        <v>-3.15673289183223</v>
+        <v>18.56603773584906</v>
+      </c>
+      <c r="AQ7">
+        <v>-1.145833333333333</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Advance Create Co., Ltd. (TSE:8798)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0143</v>
+      </c>
+      <c r="G8">
+        <v>-0.1416176470588235</v>
+      </c>
+      <c r="H8">
+        <v>-0.1416176470588235</v>
+      </c>
+      <c r="I8">
+        <v>-0.1640845439441765</v>
+      </c>
+      <c r="J8">
+        <v>-0.1640845439441765</v>
+      </c>
+      <c r="K8">
+        <v>-11.8</v>
+      </c>
+      <c r="L8">
+        <v>-0.1735294117647059</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="V8">
+        <v>0.05320924261874196</v>
+      </c>
+      <c r="W8">
+        <v>-0.2388663967611336</v>
+      </c>
+      <c r="X8">
+        <v>0.07790275218541784</v>
+      </c>
+      <c r="Y8">
+        <v>-0.3167691489465515</v>
+      </c>
+      <c r="Z8">
+        <v>1.222169911849802</v>
+      </c>
+      <c r="AA8">
+        <v>-0.200539192608169</v>
+      </c>
+      <c r="AB8">
+        <v>0.07200509732838825</v>
+      </c>
+      <c r="AC8">
+        <v>-0.2725442899365573</v>
+      </c>
+      <c r="AD8">
+        <v>15.5</v>
+      </c>
+      <c r="AE8">
+        <v>10.43874494101999</v>
+      </c>
+      <c r="AF8">
+        <v>25.93874494101999</v>
+      </c>
+      <c r="AG8">
+        <v>17.64874494101999</v>
+      </c>
+      <c r="AH8">
+        <v>0.1427254543297189</v>
+      </c>
+      <c r="AI8">
+        <v>0.454756586384247</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1017519322323221</v>
+      </c>
+      <c r="AK8">
+        <v>0.3620348577665499</v>
+      </c>
+      <c r="AL8">
+        <v>0.114</v>
+      </c>
+      <c r="AM8">
+        <v>0.101</v>
+      </c>
+      <c r="AN8">
+        <v>-2.98076923076923</v>
+      </c>
+      <c r="AO8">
+        <v>-118.4210526315789</v>
+      </c>
+      <c r="AP8">
+        <v>-3.393989411734613</v>
+      </c>
+      <c r="AQ8">
+        <v>-133.6633663366337</v>
       </c>
     </row>
   </sheetData>
